--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_214_Dominican_Republic.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_214_Dominican_Republic.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R52e5df9457ca4c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rcf4d82dc0b764dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R8824d8645edb404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbea939185c904822"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R04a359e171eb457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2da54144403840d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rb0dc15c705424897"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R73e3a8c757174dd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf8f0abe7e18849b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbfa975c192dc4ce1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rc9481b642ea84219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R9c804dd63bcb44ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ214CommercialTable" displayName="EEZ214CommercialTable" ref="A1:O9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O9"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ214CommercialTable" displayName="EEZ214CommercialTable" ref="A1:E9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E9"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ214FunctionalTable" displayName="EEZ214FunctionalTable" ref="A1:O18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O18"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ214FunctionalTable" displayName="EEZ214FunctionalTable" ref="A1:E18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E18"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ214ValidationTable" displayName="EEZ214ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ214ValidationTable" displayName="EEZ214ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6054,7 +6008,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d100fee257e422d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac47f8b06a04c07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6064,20 +6018,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6085,498 +6029,174 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>4946.614812886</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.1588734927385946</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>144.16953335361526</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>4946.614812886</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>145.23239413247626</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$81,A2,'Species'!$U$2:$U$81))</x:f>
-        <x:v>718408.7121266049</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.1588734927385946</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>144.16953335361526</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>713151.1492538556</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>5257.562872749288</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0073722981141517</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.007372298114151659</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>544.22639861</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4882099883557873</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>307.7584516580673</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>544.22639861</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>833.7528301518414</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$81,A3,'Species'!$U$2:$U$81))</x:f>
-        <x:v>453750.3000844317</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4882099883557873</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>307.7584516580673</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>167490.27378765977</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>286260.02629677195</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>2.709114325406654</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.7091143254066543</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2342.368846</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.1821229954447574</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>15.20978221147605</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2342.368846</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>15.245828053246964</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$81,A4,'Species'!$U$2:$U$81))</x:f>
-        <x:v>35711.35266339852</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.1821229954447574</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>15.20978221147605</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>35626.92000660648</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>84.43265679203614</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.002369911762689</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0023699117626889824</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>12901.218229021999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.282349468155485</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>191.57969087116055</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>12901.218229021999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>220.32171493572167</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$81,A5,'Species'!$U$2:$U$81))</x:f>
-        <x:v>2842418.524978121</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.282349468155485</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>191.57969087116055</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2471611.400177416</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>370807.1248007049</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.150026466447795</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.15002646644779508</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>29906.601327360997</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8086495278887824</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>643.6496358588687</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>29906.601327360997</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>915.9609430661353</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$81,A6,'Species'!$U$2:$U$81))</x:f>
-        <x:v>27393278.755712513</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8086495278887824</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>643.6496358588687</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>19249373.054132264</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>8143905.701580249</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.4230738153745737</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.4230738153745738</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12.441978314</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7400000000000007</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>549.5408738576253</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12.441978314</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>549.5408738576248</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$81,A7,'Species'!$U$2:$U$81))</x:f>
-        <x:v>6837.375635193177</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7400000000000007</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>549.5408738576253</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6837.375635193184</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>-7.275957614183426e-12</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>-1.064144783377526e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3462.544940919</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.113291455128477</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1298.050100470647</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3462.544940919</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1406.6022301140529</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$81,A8,'Species'!$U$2:$U$81))</x:f>
-        <x:v>4870423.435766797</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.113291455128477</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1298.050100470647</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4494556.808444039</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>375866.6273227576</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0836270723326062</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08362707233260627</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>293.99973890000007</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.481406206146598</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>3029.7458979682497</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>293.99973890000007</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3035.3621484166656</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$81,A9,'Species'!$U$2:$U$81))</x:f>
-        <x:v>892395.6791014429</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.481406206146598</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>3029.7458979682497</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>890744.5029360116</x:v>
       </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1651.1761654312722</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.001853703458162</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.001853703458161995</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G9">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O9">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R788aa68a31f243b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c71d66683c443a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6586,20 +6206,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6607,984 +6217,345 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>145.49783470699998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.636903825252334</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>433.4148877982608</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>145.49783470699998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>449.5815663758412</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$81,A2,'Species'!$U$2:$U$81))</x:f>
-        <x:v>65413.14443186628</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.636903825252334</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>433.4148877982608</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>63060.92770442429</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2352.2167274419917</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0373006997053258</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.03730069970532581</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>399.417358928</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.081579534894611</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>120.66450479453896</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>399.417358928</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>143.09383647529035</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$81,A3,'Species'!$U$2:$U$81))</x:f>
-        <x:v>57154.16224383558</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.081579534894611</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>120.66450479453896</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>48195.49782138974</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>8958.664422445836</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.1858817696135482</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.18588176961354827</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>6.220989758</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.7331069808104322</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>540.8875446739611</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>6.220989758</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>555.2072593556012</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$81,A4,'Species'!$U$2:$U$81))</x:f>
-        <x:v>3453.9386740184445</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.7331069808104322</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>540.8875446739611</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3364.8558756464795</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>89.08279837196505</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0264744766682912</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.026474476668291134</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1587.257526982</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.382872876508005</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2414.753901953762</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1587.257526982</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2559.815555507749</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$81,A5,'Species'!$U$2:$U$81))</x:f>
-        <x:v>4063086.5081652845</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.382872876508005</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2414.753901953762</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3832836.3066852633</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>230250.20148002123</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0600730589716072</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.06007305897160727</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>280.62231952300004</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.4378384748045305</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>274.05547001589065</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>280.62231952300004</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>282.6346249563596</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$81,A6,'Species'!$U$2:$U$81))</x:f>
-        <x:v>79313.58403276683</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.4378384748045305</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>274.05547001589065</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>76906.08167382522</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>2407.5023589416087</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0313044470156771</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.03130444701567725</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>471.59178964299997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.010802261568838</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1025.185043416322</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>471.59178964299997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1109.0108999304887</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$81,A7,'Species'!$U$2:$U$81))</x:f>
-        <x:v>523000.4350318131</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.010802261568838</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1025.185043416322</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>483468.84933993994</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>39531.58569187316</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.081766562097732</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.08176656209773184</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3181.922621396</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.172861471317013</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1488.8860858898393</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3181.922621396</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1505.727958158842</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$81,A8,'Species'!$U$2:$U$81))</x:f>
-        <x:v>4791109.851734029</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.172861471317013</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1488.8860858898393</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4737520.317374627</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>53589.53435940202</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0113117265508846</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.011311726550884646</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4773.570529553</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.1546070725070403</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>142.76017527973525</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4773.570529553</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>143.50302194112643</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$81,A9,'Species'!$U$2:$U$81))</x:f>
-        <x:v>685021.7964399586</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.1546070725070403</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>142.76017527973525</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>681475.7655091649</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>3546.0309307937277</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0052034585971583</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.005203458597158344</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1801.8451496</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.311020507204189</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>204.65412712678696</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1801.8451496</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>205.223729044713</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$81,A10,'Species'!$U$2:$U$81))</x:f>
-        <x:v>369781.38076204073</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.311020507204189</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>204.65412712678696</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>368755.0463090229</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1026.3344530178583</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.002783241784189</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0027832417841890983</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>15721.16843664</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.326047753203199</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>211.8594074177371</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>15721.16843664</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>213.84465323773534</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$81,A11,'Species'!$U$2:$U$81))</x:f>
-        <x:v>3361887.812825311</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.326047753203199</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>211.8594074177371</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3330677.4289009827</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>31210.383924328256</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.009370581387891</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.009370581387891017</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>6439.541017317</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.131529014986902</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1353.7205290099707</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>6439.541017317</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1423.4089077886404</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$81,A12,'Species'!$U$2:$U$81))</x:f>
-        <x:v>9166100.046119342</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.131529014986902</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1353.7205290099707</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>8717338.872543775</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>448761.1735755671</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.051479147494081</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.051479147494081036</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>15119.712350480997</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.8017449728894763</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>633.497598523326</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>15119.712350480997</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>872.4938685264744</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$81,A13,'Species'!$U$2:$U$81))</x:f>
-        <x:v>13191856.31967868</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.8017449728894763</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>633.497598523326</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>9578301.464393185</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>3613554.8552854937</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.3772646819186771</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.37726468191867707</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2342.368846</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.1821229954447574</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>15.20978221147605</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2342.368846</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>15.245828053246964</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$81,A14,'Species'!$U$2:$U$81))</x:f>
-        <x:v>35711.35266339852</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.1821229954447574</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>15.20978221147605</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>35626.92000660648</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>84.43265679203614</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.002369911762689</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.0023699117626889824</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>173.04428333299998</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.2765662445115478</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>189.0454567083485</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>173.04428333299998</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>192.93856487820327</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$81,A15,'Species'!$U$2:$U$81))</x:f>
-        <x:v>33386.91568664621</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.2765662445115478</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>189.0454567083485</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>32713.23557345584</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>673.6801131903667</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0205935029470763</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.02059350294707638</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>108.49867</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.0300000000000002</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>107.1519305237607</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>108.49867</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>107.1519305237606</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$81,A16,'Species'!$U$2:$U$81))</x:f>
-        <x:v>11625.841949760428</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.0300000000000002</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>107.1519305237607</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>11625.84194976044</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>-1.0913936421275139e-11</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>0.9999999999999991</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>-9.38765249728862e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>544.22639861</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.4882099883557873</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>307.7584516580673</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>544.22639861</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>833.7528301518414</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$81,A17,'Species'!$U$2:$U$81))</x:f>
-        <x:v>453750.3000844317</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.4882099883557873</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>307.7584516580673</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>167490.27378765977</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>286260.02629677195</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>2.709114325406654</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>1.7091143254066543</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1313.5101495410001</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.2829658296182034</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>191.85177853461778</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1313.5101495410001</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>244.8178612534447</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$81,A18,'Species'!$U$2:$U$81))</x:f>
-        <x:v>321570.74554532</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.2829658296182034</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>191.85177853461778</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>251999.25831271263</x:v>
       </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>69571.48723260735</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.2760781428422865</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.2760781428422866</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O18">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R552e3ebc708942ad"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R303ad0106b9948aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7759,7 +6730,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -7858,7 +6829,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>37213224.13606851</x:v>
+        <x:v>28029391.484373044</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7872,7 +6843,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>37213224.1360685</x:v>
+        <x:v>32421356.943761438</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7886,7 +6857,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-9183832.651695464</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7900,7 +6871,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-4791867.19230707</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7911,9 +6882,9 @@
         <x:v>EEZ_214</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7925,47 +6896,19 @@
         <x:v>EEZ_214</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_214</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_214</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fe6484ba3b54cbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51daf8ddc90b45ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8012,7 +6955,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
